--- a/12610764.xlsx
+++ b/12610764.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F93277E-D606-4C73-B7FD-1520AAD11DFB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EEF87225-B2A5-4537-BDEE-40E32C1FFD91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="85">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -2635,26 +2635,50 @@
       </c>
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A40" s="13"/>
-      <c r="B40" s="14"/>
-      <c r="C40" s="14"/>
-      <c r="D40" s="14"/>
-      <c r="E40" s="14"/>
-      <c r="F40" s="14"/>
-      <c r="G40" s="14"/>
-      <c r="H40" s="14"/>
-      <c r="I40" s="15" t="str">
+      <c r="A40" s="13">
+        <v>46278</v>
+      </c>
+      <c r="B40" s="14">
+        <v>200</v>
+      </c>
+      <c r="C40" s="14">
+        <v>60</v>
+      </c>
+      <c r="D40" s="14">
+        <v>300</v>
+      </c>
+      <c r="E40" s="14">
+        <v>120</v>
+      </c>
+      <c r="F40" s="14">
+        <v>0</v>
+      </c>
+      <c r="G40" s="14">
+        <v>0</v>
+      </c>
+      <c r="H40" s="14">
+        <v>300</v>
+      </c>
+      <c r="I40" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J40" s="15" t="str">
+        <v>980</v>
+      </c>
+      <c r="J40" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K40" s="16"/>
-      <c r="L40" s="16"/>
-      <c r="M40" s="16"/>
-      <c r="N40" s="17"/>
+        <v>460</v>
+      </c>
+      <c r="K40" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="L40" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M40" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="N40" s="17" t="s">
+        <v>71</v>
+      </c>
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A41" s="13"/>

--- a/12610764.xlsx
+++ b/12610764.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EEF87225-B2A5-4537-BDEE-40E32C1FFD91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1932952C-E52A-495A-8BCB-ACC518715D31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="86">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -290,6 +290,9 @@
   </si>
   <si>
     <t>Very bad day.</t>
+  </si>
+  <si>
+    <t>Today day is very boring.</t>
   </si>
 </sst>
 </file>
@@ -2681,26 +2684,50 @@
       </c>
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A41" s="13"/>
-      <c r="B41" s="14"/>
-      <c r="C41" s="14"/>
-      <c r="D41" s="14"/>
-      <c r="E41" s="14"/>
-      <c r="F41" s="14"/>
-      <c r="G41" s="14"/>
-      <c r="H41" s="14"/>
-      <c r="I41" s="15" t="str">
+      <c r="A41" s="13">
+        <v>46280</v>
+      </c>
+      <c r="B41" s="14">
+        <v>200</v>
+      </c>
+      <c r="C41" s="14">
+        <v>120</v>
+      </c>
+      <c r="D41" s="14">
+        <v>300</v>
+      </c>
+      <c r="E41" s="14">
+        <v>120</v>
+      </c>
+      <c r="F41" s="14">
+        <v>350</v>
+      </c>
+      <c r="G41" s="14">
+        <v>7</v>
+      </c>
+      <c r="H41" s="14">
+        <v>300</v>
+      </c>
+      <c r="I41" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J41" s="15" t="str">
+        <v>1390</v>
+      </c>
+      <c r="J41" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K41" s="16"/>
-      <c r="L41" s="16"/>
-      <c r="M41" s="16"/>
-      <c r="N41" s="17"/>
+        <v>50</v>
+      </c>
+      <c r="K41" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L41" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M41" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="N41" s="17" t="s">
+        <v>85</v>
+      </c>
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A42" s="13"/>

--- a/12610764.xlsx
+++ b/12610764.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1932952C-E52A-495A-8BCB-ACC518715D31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7AF0C57-8676-4732-8113-FE3EF505F909}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="88">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -293,6 +293,12 @@
   </si>
   <si>
     <t>Today day is very boring.</t>
+  </si>
+  <si>
+    <t>All good.</t>
+  </si>
+  <si>
+    <t>Moody day.</t>
   </si>
 </sst>
 </file>
@@ -2730,48 +2736,96 @@
       </c>
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A42" s="13"/>
-      <c r="B42" s="14"/>
-      <c r="C42" s="14"/>
-      <c r="D42" s="14"/>
-      <c r="E42" s="14"/>
-      <c r="F42" s="14"/>
-      <c r="G42" s="14"/>
-      <c r="H42" s="14"/>
-      <c r="I42" s="15" t="str">
+      <c r="A42" s="13">
+        <v>46281</v>
+      </c>
+      <c r="B42" s="14">
+        <v>250</v>
+      </c>
+      <c r="C42" s="14">
+        <v>60</v>
+      </c>
+      <c r="D42" s="14">
+        <v>200</v>
+      </c>
+      <c r="E42" s="14">
+        <v>60</v>
+      </c>
+      <c r="F42" s="14">
+        <v>300</v>
+      </c>
+      <c r="G42" s="14">
+        <v>6</v>
+      </c>
+      <c r="H42" s="14">
+        <v>200</v>
+      </c>
+      <c r="I42" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J42" s="15" t="str">
+        <v>1070</v>
+      </c>
+      <c r="J42" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K42" s="16"/>
-      <c r="L42" s="16"/>
-      <c r="M42" s="16"/>
-      <c r="N42" s="17"/>
+        <v>370</v>
+      </c>
+      <c r="K42" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="L42" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M42" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="N42" s="17" t="s">
+        <v>86</v>
+      </c>
     </row>
     <row r="43" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A43" s="13"/>
-      <c r="B43" s="14"/>
-      <c r="C43" s="14"/>
-      <c r="D43" s="14"/>
-      <c r="E43" s="14"/>
-      <c r="F43" s="14"/>
-      <c r="G43" s="14"/>
-      <c r="H43" s="14"/>
-      <c r="I43" s="15" t="str">
+      <c r="A43" s="13">
+        <v>46282</v>
+      </c>
+      <c r="B43" s="14">
+        <v>200</v>
+      </c>
+      <c r="C43" s="14">
+        <v>45</v>
+      </c>
+      <c r="D43" s="14">
+        <v>300</v>
+      </c>
+      <c r="E43" s="14">
+        <v>120</v>
+      </c>
+      <c r="F43" s="14">
+        <v>150</v>
+      </c>
+      <c r="G43" s="14">
+        <v>3</v>
+      </c>
+      <c r="H43" s="14">
+        <v>300</v>
+      </c>
+      <c r="I43" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J43" s="15" t="str">
+        <v>1115</v>
+      </c>
+      <c r="J43" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K43" s="16"/>
-      <c r="L43" s="16"/>
-      <c r="M43" s="16"/>
-      <c r="N43" s="17"/>
+        <v>325</v>
+      </c>
+      <c r="K43" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L43" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="M43" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="N43" s="17" t="s">
+        <v>87</v>
+      </c>
     </row>
     <row r="44" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A44" s="13"/>

--- a/12610764.xlsx
+++ b/12610764.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7AF0C57-8676-4732-8113-FE3EF505F909}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5C35667-0676-4151-9BDA-EFC28AB962D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="89">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -299,6 +299,9 @@
   </si>
   <si>
     <t>Moody day.</t>
+  </si>
+  <si>
+    <t>Preparation for CA.</t>
   </si>
 </sst>
 </file>
@@ -2828,26 +2831,50 @@
       </c>
     </row>
     <row r="44" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A44" s="13"/>
-      <c r="B44" s="14"/>
-      <c r="C44" s="14"/>
-      <c r="D44" s="14"/>
-      <c r="E44" s="14"/>
-      <c r="F44" s="14"/>
-      <c r="G44" s="14"/>
-      <c r="H44" s="14"/>
-      <c r="I44" s="15" t="str">
+      <c r="A44" s="13">
+        <v>46283</v>
+      </c>
+      <c r="B44" s="14">
+        <v>300</v>
+      </c>
+      <c r="C44" s="14">
+        <v>120</v>
+      </c>
+      <c r="D44" s="14">
+        <v>300</v>
+      </c>
+      <c r="E44" s="14">
+        <v>60</v>
+      </c>
+      <c r="F44" s="14">
+        <v>250</v>
+      </c>
+      <c r="G44" s="14">
+        <v>5</v>
+      </c>
+      <c r="H44" s="14">
+        <v>200</v>
+      </c>
+      <c r="I44" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J44" s="15" t="str">
+        <v>1230</v>
+      </c>
+      <c r="J44" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K44" s="16"/>
-      <c r="L44" s="16"/>
-      <c r="M44" s="16"/>
-      <c r="N44" s="17"/>
+        <v>210</v>
+      </c>
+      <c r="K44" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L44" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="M44" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="N44" s="17" t="s">
+        <v>88</v>
+      </c>
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A45" s="13"/>

--- a/12610764.xlsx
+++ b/12610764.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5C35667-0676-4151-9BDA-EFC28AB962D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{978ED46C-4ED1-4162-A8FF-ADE43877E4D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="90">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -302,6 +302,9 @@
   </si>
   <si>
     <t>Preparation for CA.</t>
+  </si>
+  <si>
+    <t>Explore agriculture department.</t>
   </si>
 </sst>
 </file>
@@ -2877,26 +2880,50 @@
       </c>
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A45" s="13"/>
-      <c r="B45" s="14"/>
-      <c r="C45" s="14"/>
-      <c r="D45" s="14"/>
-      <c r="E45" s="14"/>
-      <c r="F45" s="14"/>
-      <c r="G45" s="14"/>
-      <c r="H45" s="14"/>
-      <c r="I45" s="15" t="str">
+      <c r="A45" s="13">
+        <v>46284</v>
+      </c>
+      <c r="B45" s="14">
+        <v>120</v>
+      </c>
+      <c r="C45" s="14">
+        <v>120</v>
+      </c>
+      <c r="D45" s="14">
+        <v>300</v>
+      </c>
+      <c r="E45" s="14">
+        <v>120</v>
+      </c>
+      <c r="F45" s="14">
+        <v>0</v>
+      </c>
+      <c r="G45" s="14">
+        <v>0</v>
+      </c>
+      <c r="H45" s="14">
+        <v>200</v>
+      </c>
+      <c r="I45" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J45" s="15" t="str">
+        <v>860</v>
+      </c>
+      <c r="J45" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K45" s="16"/>
-      <c r="L45" s="16"/>
-      <c r="M45" s="16"/>
-      <c r="N45" s="17"/>
+        <v>580</v>
+      </c>
+      <c r="K45" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="L45" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="M45" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="N45" s="17" t="s">
+        <v>89</v>
+      </c>
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A46" s="13"/>

--- a/12610764.xlsx
+++ b/12610764.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{978ED46C-4ED1-4162-A8FF-ADE43877E4D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71CC5C88-1DD2-42AD-8A15-4D41FE49027B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="91">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -305,6 +305,9 @@
   </si>
   <si>
     <t>Explore agriculture department.</t>
+  </si>
+  <si>
+    <t>Peaceful day.</t>
   </si>
 </sst>
 </file>
@@ -2926,26 +2929,50 @@
       </c>
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A46" s="13"/>
-      <c r="B46" s="14"/>
-      <c r="C46" s="14"/>
-      <c r="D46" s="14"/>
-      <c r="E46" s="14"/>
-      <c r="F46" s="14"/>
-      <c r="G46" s="14"/>
-      <c r="H46" s="14"/>
-      <c r="I46" s="15" t="str">
+      <c r="A46" s="13">
+        <v>46285</v>
+      </c>
+      <c r="B46" s="14">
+        <v>300</v>
+      </c>
+      <c r="C46" s="14">
+        <v>120</v>
+      </c>
+      <c r="D46" s="14">
+        <v>400</v>
+      </c>
+      <c r="E46" s="14">
+        <v>120</v>
+      </c>
+      <c r="F46" s="14">
+        <v>0</v>
+      </c>
+      <c r="G46" s="14">
+        <v>0</v>
+      </c>
+      <c r="H46" s="14">
+        <v>300</v>
+      </c>
+      <c r="I46" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J46" s="15" t="str">
+        <v>1240</v>
+      </c>
+      <c r="J46" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K46" s="16"/>
-      <c r="L46" s="16"/>
-      <c r="M46" s="16"/>
-      <c r="N46" s="17"/>
+        <v>200</v>
+      </c>
+      <c r="K46" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L46" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="M46" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="N46" s="17" t="s">
+        <v>90</v>
+      </c>
     </row>
     <row r="47" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A47" s="13"/>

--- a/12610764.xlsx
+++ b/12610764.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71CC5C88-1DD2-42AD-8A15-4D41FE49027B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F4A9EC9-FC24-4003-AE6C-2D5D1E5E54DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="91">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -2975,26 +2975,50 @@
       </c>
     </row>
     <row r="47" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A47" s="13"/>
-      <c r="B47" s="14"/>
-      <c r="C47" s="14"/>
-      <c r="D47" s="14"/>
-      <c r="E47" s="14"/>
-      <c r="F47" s="14"/>
-      <c r="G47" s="14"/>
-      <c r="H47" s="14"/>
-      <c r="I47" s="15" t="str">
+      <c r="A47" s="13">
+        <v>46286</v>
+      </c>
+      <c r="B47" s="14">
+        <v>200</v>
+      </c>
+      <c r="C47" s="14">
+        <v>60</v>
+      </c>
+      <c r="D47" s="14">
+        <v>300</v>
+      </c>
+      <c r="E47" s="14">
+        <v>180</v>
+      </c>
+      <c r="F47" s="14">
+        <v>300</v>
+      </c>
+      <c r="G47" s="14">
+        <v>6</v>
+      </c>
+      <c r="H47" s="14">
+        <v>200</v>
+      </c>
+      <c r="I47" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J47" s="15" t="str">
+        <v>1240</v>
+      </c>
+      <c r="J47" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K47" s="16"/>
-      <c r="L47" s="16"/>
-      <c r="M47" s="16"/>
-      <c r="N47" s="17"/>
+        <v>200</v>
+      </c>
+      <c r="K47" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="L47" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="M47" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="N47" s="17" t="s">
+        <v>74</v>
+      </c>
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A48" s="13"/>

--- a/12610764.xlsx
+++ b/12610764.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F4A9EC9-FC24-4003-AE6C-2D5D1E5E54DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{199443D5-CBB9-4B9C-A39C-D4B22231CC4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="91">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -3021,26 +3021,50 @@
       </c>
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A48" s="13"/>
-      <c r="B48" s="14"/>
-      <c r="C48" s="14"/>
-      <c r="D48" s="14"/>
-      <c r="E48" s="14"/>
-      <c r="F48" s="14"/>
-      <c r="G48" s="14"/>
-      <c r="H48" s="14"/>
-      <c r="I48" s="15" t="str">
+      <c r="A48" s="13">
+        <v>46287</v>
+      </c>
+      <c r="B48" s="14">
+        <v>300</v>
+      </c>
+      <c r="C48" s="14">
+        <v>30</v>
+      </c>
+      <c r="D48" s="14">
+        <v>300</v>
+      </c>
+      <c r="E48" s="14">
+        <v>120</v>
+      </c>
+      <c r="F48" s="14">
+        <v>350</v>
+      </c>
+      <c r="G48" s="14">
+        <v>7</v>
+      </c>
+      <c r="H48" s="14">
+        <v>200</v>
+      </c>
+      <c r="I48" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J48" s="15" t="str">
+        <v>1300</v>
+      </c>
+      <c r="J48" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K48" s="16"/>
-      <c r="L48" s="16"/>
-      <c r="M48" s="16"/>
-      <c r="N48" s="17"/>
+        <v>140</v>
+      </c>
+      <c r="K48" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L48" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="M48" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="N48" s="17" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A49" s="13"/>

--- a/12610764.xlsx
+++ b/12610764.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{199443D5-CBB9-4B9C-A39C-D4B22231CC4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F646FFC8-4548-4ED3-8F62-97F8D545A145}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="229" uniqueCount="92">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -308,6 +308,9 @@
   </si>
   <si>
     <t>Peaceful day.</t>
+  </si>
+  <si>
+    <t>Learning new things.</t>
   </si>
 </sst>
 </file>
@@ -3067,26 +3070,50 @@
       </c>
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A49" s="13"/>
-      <c r="B49" s="14"/>
-      <c r="C49" s="14"/>
-      <c r="D49" s="14"/>
-      <c r="E49" s="14"/>
-      <c r="F49" s="14"/>
-      <c r="G49" s="14"/>
-      <c r="H49" s="14"/>
-      <c r="I49" s="15" t="str">
+      <c r="A49" s="13">
+        <v>46288</v>
+      </c>
+      <c r="B49" s="14">
+        <v>300</v>
+      </c>
+      <c r="C49" s="14">
+        <v>60</v>
+      </c>
+      <c r="D49" s="14">
+        <v>300</v>
+      </c>
+      <c r="E49" s="14">
+        <v>60</v>
+      </c>
+      <c r="F49" s="14">
+        <v>300</v>
+      </c>
+      <c r="G49" s="14">
+        <v>6</v>
+      </c>
+      <c r="H49" s="14">
+        <v>180</v>
+      </c>
+      <c r="I49" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J49" s="15" t="str">
+        <v>1200</v>
+      </c>
+      <c r="J49" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K49" s="16"/>
-      <c r="L49" s="16"/>
-      <c r="M49" s="16"/>
-      <c r="N49" s="17"/>
+        <v>240</v>
+      </c>
+      <c r="K49" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="L49" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M49" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="N49" s="17" t="s">
+        <v>91</v>
+      </c>
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A50" s="13"/>

--- a/12610764.xlsx
+++ b/12610764.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F646FFC8-4548-4ED3-8F62-97F8D545A145}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA0EF15C-427A-4B44-8C3B-78C0C3315C35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="229" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="92">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -3116,26 +3116,50 @@
       </c>
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A50" s="13"/>
-      <c r="B50" s="14"/>
-      <c r="C50" s="14"/>
-      <c r="D50" s="14"/>
-      <c r="E50" s="14"/>
-      <c r="F50" s="14"/>
-      <c r="G50" s="14"/>
-      <c r="H50" s="14"/>
-      <c r="I50" s="15" t="str">
+      <c r="A50" s="13">
+        <v>46289</v>
+      </c>
+      <c r="B50" s="14">
+        <v>300</v>
+      </c>
+      <c r="C50" s="14">
+        <v>60</v>
+      </c>
+      <c r="D50" s="14">
+        <v>300</v>
+      </c>
+      <c r="E50" s="14">
+        <v>240</v>
+      </c>
+      <c r="F50" s="14">
+        <v>100</v>
+      </c>
+      <c r="G50" s="14">
+        <v>2</v>
+      </c>
+      <c r="H50" s="14">
+        <v>200</v>
+      </c>
+      <c r="I50" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J50" s="15" t="str">
+        <v>1200</v>
+      </c>
+      <c r="J50" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K50" s="16"/>
-      <c r="L50" s="16"/>
-      <c r="M50" s="16"/>
-      <c r="N50" s="17"/>
+        <v>240</v>
+      </c>
+      <c r="K50" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L50" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M50" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="N50" s="17" t="s">
+        <v>60</v>
+      </c>
     </row>
     <row r="51" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A51" s="13"/>

--- a/12610764.xlsx
+++ b/12610764.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA0EF15C-427A-4B44-8C3B-78C0C3315C35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5836D11A-489E-4462-89D2-B3E63AACC96A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="237" uniqueCount="92">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -3162,26 +3162,50 @@
       </c>
     </row>
     <row r="51" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A51" s="13"/>
-      <c r="B51" s="14"/>
-      <c r="C51" s="14"/>
-      <c r="D51" s="14"/>
-      <c r="E51" s="14"/>
-      <c r="F51" s="14"/>
-      <c r="G51" s="14"/>
-      <c r="H51" s="14"/>
-      <c r="I51" s="15" t="str">
+      <c r="A51" s="13">
+        <v>46290</v>
+      </c>
+      <c r="B51" s="14">
+        <v>300</v>
+      </c>
+      <c r="C51" s="14">
+        <v>45</v>
+      </c>
+      <c r="D51" s="14">
+        <v>300</v>
+      </c>
+      <c r="E51" s="14">
+        <v>200</v>
+      </c>
+      <c r="F51" s="14">
+        <v>250</v>
+      </c>
+      <c r="G51" s="14">
+        <v>5</v>
+      </c>
+      <c r="H51" s="14">
+        <v>200</v>
+      </c>
+      <c r="I51" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J51" s="15" t="str">
+        <v>1295</v>
+      </c>
+      <c r="J51" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K51" s="16"/>
-      <c r="L51" s="16"/>
-      <c r="M51" s="16"/>
-      <c r="N51" s="17"/>
+        <v>145</v>
+      </c>
+      <c r="K51" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="L51" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M51" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="N51" s="17" t="s">
+        <v>74</v>
+      </c>
     </row>
     <row r="52" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A52" s="13"/>

--- a/12610764.xlsx
+++ b/12610764.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5836D11A-489E-4462-89D2-B3E63AACC96A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65CD0E38-2E75-4529-B14B-AF4A1F81C983}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="237" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="241" uniqueCount="92">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -3208,26 +3208,50 @@
       </c>
     </row>
     <row r="52" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A52" s="13"/>
-      <c r="B52" s="14"/>
-      <c r="C52" s="14"/>
-      <c r="D52" s="14"/>
-      <c r="E52" s="14"/>
-      <c r="F52" s="14"/>
-      <c r="G52" s="14"/>
-      <c r="H52" s="14"/>
-      <c r="I52" s="15" t="str">
+      <c r="A52" s="13">
+        <v>46291</v>
+      </c>
+      <c r="B52" s="14">
+        <v>300</v>
+      </c>
+      <c r="C52" s="14">
+        <v>30</v>
+      </c>
+      <c r="D52" s="14">
+        <v>360</v>
+      </c>
+      <c r="E52" s="14">
+        <v>200</v>
+      </c>
+      <c r="F52" s="14">
+        <v>150</v>
+      </c>
+      <c r="G52" s="14">
+        <v>3</v>
+      </c>
+      <c r="H52" s="14">
+        <v>300</v>
+      </c>
+      <c r="I52" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J52" s="15" t="str">
+        <v>1340</v>
+      </c>
+      <c r="J52" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K52" s="16"/>
-      <c r="L52" s="16"/>
-      <c r="M52" s="16"/>
-      <c r="N52" s="17"/>
+        <v>100</v>
+      </c>
+      <c r="K52" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="L52" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M52" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="N52" s="17" t="s">
+        <v>90</v>
+      </c>
     </row>
     <row r="53" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A53" s="13"/>

--- a/12610764.xlsx
+++ b/12610764.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65CD0E38-2E75-4529-B14B-AF4A1F81C983}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C35B01E3-A29E-40A0-9F4B-C9847397D36C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="241" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="245" uniqueCount="92">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -3254,26 +3254,50 @@
       </c>
     </row>
     <row r="53" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A53" s="13"/>
-      <c r="B53" s="14"/>
-      <c r="C53" s="14"/>
-      <c r="D53" s="14"/>
-      <c r="E53" s="14"/>
-      <c r="F53" s="14"/>
-      <c r="G53" s="14"/>
-      <c r="H53" s="14"/>
-      <c r="I53" s="15" t="str">
+      <c r="A53" s="13">
+        <v>46292</v>
+      </c>
+      <c r="B53" s="14">
+        <v>360</v>
+      </c>
+      <c r="C53" s="14">
+        <v>30</v>
+      </c>
+      <c r="D53" s="14">
+        <v>300</v>
+      </c>
+      <c r="E53" s="14">
+        <v>60</v>
+      </c>
+      <c r="F53" s="14">
+        <v>0</v>
+      </c>
+      <c r="G53" s="14">
+        <v>0</v>
+      </c>
+      <c r="H53" s="14">
+        <v>200</v>
+      </c>
+      <c r="I53" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J53" s="15" t="str">
+        <v>950</v>
+      </c>
+      <c r="J53" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K53" s="16"/>
-      <c r="L53" s="16"/>
-      <c r="M53" s="16"/>
-      <c r="N53" s="17"/>
+        <v>490</v>
+      </c>
+      <c r="K53" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="L53" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="M53" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="N53" s="17" t="s">
+        <v>71</v>
+      </c>
     </row>
     <row r="54" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A54" s="13"/>

--- a/12610764.xlsx
+++ b/12610764.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C35B01E3-A29E-40A0-9F4B-C9847397D36C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A43B82B3-B11F-4F88-A619-2FBE803B2B9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="245" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="249" uniqueCount="93">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -311,6 +311,9 @@
   </si>
   <si>
     <t>Learning new things.</t>
+  </si>
+  <si>
+    <t>Bad day.</t>
   </si>
 </sst>
 </file>
@@ -3300,26 +3303,50 @@
       </c>
     </row>
     <row r="54" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A54" s="13"/>
-      <c r="B54" s="14"/>
-      <c r="C54" s="14"/>
-      <c r="D54" s="14"/>
-      <c r="E54" s="14"/>
-      <c r="F54" s="14"/>
-      <c r="G54" s="14"/>
-      <c r="H54" s="14"/>
-      <c r="I54" s="15" t="str">
+      <c r="A54" s="13">
+        <v>46293</v>
+      </c>
+      <c r="B54" s="14">
+        <v>400</v>
+      </c>
+      <c r="C54" s="14">
+        <v>30</v>
+      </c>
+      <c r="D54" s="14">
+        <v>200</v>
+      </c>
+      <c r="E54" s="14">
+        <v>0</v>
+      </c>
+      <c r="F54" s="14">
+        <v>0</v>
+      </c>
+      <c r="G54" s="14">
+        <v>0</v>
+      </c>
+      <c r="H54" s="14">
+        <v>300</v>
+      </c>
+      <c r="I54" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J54" s="15" t="str">
+        <v>930</v>
+      </c>
+      <c r="J54" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K54" s="16"/>
-      <c r="L54" s="16"/>
-      <c r="M54" s="16"/>
-      <c r="N54" s="17"/>
+        <v>510</v>
+      </c>
+      <c r="K54" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="L54" s="16" t="s">
+        <v>73</v>
+      </c>
+      <c r="M54" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="N54" s="17" t="s">
+        <v>92</v>
+      </c>
     </row>
     <row r="55" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A55" s="13"/>

--- a/12610764.xlsx
+++ b/12610764.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A43B82B3-B11F-4F88-A619-2FBE803B2B9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7D02B94-EC28-42AE-9D46-B688FF258E44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="249" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="253" uniqueCount="93">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -3349,26 +3349,50 @@
       </c>
     </row>
     <row r="55" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A55" s="13"/>
-      <c r="B55" s="14"/>
-      <c r="C55" s="14"/>
-      <c r="D55" s="14"/>
-      <c r="E55" s="14"/>
-      <c r="F55" s="14"/>
-      <c r="G55" s="14"/>
-      <c r="H55" s="14"/>
-      <c r="I55" s="15" t="str">
+      <c r="A55" s="13">
+        <v>46294</v>
+      </c>
+      <c r="B55" s="14">
+        <v>400</v>
+      </c>
+      <c r="C55" s="14">
+        <v>30</v>
+      </c>
+      <c r="D55" s="14">
+        <v>200</v>
+      </c>
+      <c r="E55" s="14">
+        <v>60</v>
+      </c>
+      <c r="F55" s="14">
+        <v>0</v>
+      </c>
+      <c r="G55" s="14">
+        <v>0</v>
+      </c>
+      <c r="H55" s="14">
+        <v>200</v>
+      </c>
+      <c r="I55" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J55" s="15" t="str">
+        <v>890</v>
+      </c>
+      <c r="J55" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K55" s="16"/>
-      <c r="L55" s="16"/>
-      <c r="M55" s="16"/>
-      <c r="N55" s="17"/>
+        <v>550</v>
+      </c>
+      <c r="K55" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L55" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M55" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="N55" s="17" t="s">
+        <v>74</v>
+      </c>
     </row>
     <row r="56" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A56" s="13"/>

--- a/12610764.xlsx
+++ b/12610764.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7D02B94-EC28-42AE-9D46-B688FF258E44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C154A7A1-A09C-4196-A8CA-0CF25A24374D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="253" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="94">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -314,6 +314,9 @@
   </si>
   <si>
     <t>Bad day.</t>
+  </si>
+  <si>
+    <t>All things are good.</t>
   </si>
 </sst>
 </file>
@@ -3395,26 +3398,50 @@
       </c>
     </row>
     <row r="56" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A56" s="13"/>
-      <c r="B56" s="14"/>
-      <c r="C56" s="14"/>
-      <c r="D56" s="14"/>
-      <c r="E56" s="14"/>
-      <c r="F56" s="14"/>
-      <c r="G56" s="14"/>
-      <c r="H56" s="14"/>
-      <c r="I56" s="15" t="str">
+      <c r="A56" s="13">
+        <v>46295</v>
+      </c>
+      <c r="B56" s="14">
+        <v>400</v>
+      </c>
+      <c r="C56" s="14">
+        <v>30</v>
+      </c>
+      <c r="D56" s="14">
+        <v>300</v>
+      </c>
+      <c r="E56" s="14">
+        <v>120</v>
+      </c>
+      <c r="F56" s="14">
+        <v>0</v>
+      </c>
+      <c r="G56" s="14">
+        <v>0</v>
+      </c>
+      <c r="H56" s="14">
+        <v>200</v>
+      </c>
+      <c r="I56" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J56" s="15" t="str">
+        <v>1050</v>
+      </c>
+      <c r="J56" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K56" s="16"/>
-      <c r="L56" s="16"/>
-      <c r="M56" s="16"/>
-      <c r="N56" s="17"/>
+        <v>390</v>
+      </c>
+      <c r="K56" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="L56" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="M56" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="N56" s="17" t="s">
+        <v>93</v>
+      </c>
     </row>
     <row r="57" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A57" s="13"/>

--- a/12610764.xlsx
+++ b/12610764.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C154A7A1-A09C-4196-A8CA-0CF25A24374D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5410E8E2-4AE4-4B2E-87DD-2B0A2950C08A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="265" uniqueCount="95">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -317,6 +317,9 @@
   </si>
   <si>
     <t>All things are good.</t>
+  </si>
+  <si>
+    <t>Explore Golden Temple.</t>
   </si>
 </sst>
 </file>
@@ -3444,48 +3447,96 @@
       </c>
     </row>
     <row r="57" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A57" s="13"/>
-      <c r="B57" s="14"/>
-      <c r="C57" s="14"/>
-      <c r="D57" s="14"/>
-      <c r="E57" s="14"/>
-      <c r="F57" s="14"/>
-      <c r="G57" s="14"/>
-      <c r="H57" s="14"/>
-      <c r="I57" s="15" t="str">
+      <c r="A57" s="13">
+        <v>46296</v>
+      </c>
+      <c r="B57" s="14">
+        <v>300</v>
+      </c>
+      <c r="C57" s="14">
+        <v>120</v>
+      </c>
+      <c r="D57" s="14">
+        <v>0</v>
+      </c>
+      <c r="E57" s="14">
+        <v>0</v>
+      </c>
+      <c r="F57" s="14">
+        <v>0</v>
+      </c>
+      <c r="G57" s="14">
+        <v>0</v>
+      </c>
+      <c r="H57" s="14">
+        <v>600</v>
+      </c>
+      <c r="I57" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J57" s="15" t="str">
+        <v>1020</v>
+      </c>
+      <c r="J57" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K57" s="16"/>
-      <c r="L57" s="16"/>
-      <c r="M57" s="16"/>
-      <c r="N57" s="17"/>
+        <v>420</v>
+      </c>
+      <c r="K57" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L57" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M57" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="N57" s="17" t="s">
+        <v>94</v>
+      </c>
     </row>
     <row r="58" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A58" s="13"/>
-      <c r="B58" s="14"/>
-      <c r="C58" s="14"/>
-      <c r="D58" s="14"/>
-      <c r="E58" s="14"/>
-      <c r="F58" s="14"/>
-      <c r="G58" s="14"/>
-      <c r="H58" s="14"/>
-      <c r="I58" s="15" t="str">
+      <c r="A58" s="13">
+        <v>46297</v>
+      </c>
+      <c r="B58" s="14">
+        <v>600</v>
+      </c>
+      <c r="C58" s="14">
+        <v>60</v>
+      </c>
+      <c r="D58" s="14">
+        <v>0</v>
+      </c>
+      <c r="E58" s="14">
+        <v>0</v>
+      </c>
+      <c r="F58" s="14">
+        <v>0</v>
+      </c>
+      <c r="G58" s="14">
+        <v>0</v>
+      </c>
+      <c r="H58" s="14">
+        <v>200</v>
+      </c>
+      <c r="I58" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J58" s="15" t="str">
+        <v>860</v>
+      </c>
+      <c r="J58" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K58" s="16"/>
-      <c r="L58" s="16"/>
-      <c r="M58" s="16"/>
-      <c r="N58" s="17"/>
+        <v>580</v>
+      </c>
+      <c r="K58" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="L58" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="M58" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="N58" s="17" t="s">
+        <v>71</v>
+      </c>
     </row>
     <row r="59" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A59" s="13"/>

--- a/12610764.xlsx
+++ b/12610764.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5410E8E2-4AE4-4B2E-87DD-2B0A2950C08A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4EB84EE3-E7E0-413C-B096-4A8669B18021}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="265" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="269" uniqueCount="96">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -320,6 +320,9 @@
   </si>
   <si>
     <t>Explore Golden Temple.</t>
+  </si>
+  <si>
+    <t>Lazy Day.</t>
   </si>
 </sst>
 </file>
@@ -3539,26 +3542,50 @@
       </c>
     </row>
     <row r="59" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A59" s="13"/>
-      <c r="B59" s="14"/>
-      <c r="C59" s="14"/>
-      <c r="D59" s="14"/>
-      <c r="E59" s="14"/>
-      <c r="F59" s="14"/>
-      <c r="G59" s="14"/>
-      <c r="H59" s="14"/>
-      <c r="I59" s="15" t="str">
+      <c r="A59" s="13">
+        <v>46298</v>
+      </c>
+      <c r="B59" s="14">
+        <v>420</v>
+      </c>
+      <c r="C59" s="14">
+        <v>30</v>
+      </c>
+      <c r="D59" s="14">
+        <v>120</v>
+      </c>
+      <c r="E59" s="14">
+        <v>60</v>
+      </c>
+      <c r="F59" s="14">
+        <v>0</v>
+      </c>
+      <c r="G59" s="14">
+        <v>0</v>
+      </c>
+      <c r="H59" s="14">
+        <v>300</v>
+      </c>
+      <c r="I59" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J59" s="15" t="str">
+        <v>930</v>
+      </c>
+      <c r="J59" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K59" s="16"/>
-      <c r="L59" s="16"/>
-      <c r="M59" s="16"/>
-      <c r="N59" s="17"/>
+        <v>510</v>
+      </c>
+      <c r="K59" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="L59" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="M59" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="N59" s="17" t="s">
+        <v>95</v>
+      </c>
     </row>
     <row r="60" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A60" s="13"/>

--- a/12610764.xlsx
+++ b/12610764.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4EB84EE3-E7E0-413C-B096-4A8669B18021}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{121E204C-CB79-4AA6-94AE-06DE2938597D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="269" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="273" uniqueCount="97">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -323,6 +323,9 @@
   </si>
   <si>
     <t>Lazy Day.</t>
+  </si>
+  <si>
+    <t>Making minor Project.</t>
   </si>
 </sst>
 </file>
@@ -3588,26 +3591,50 @@
       </c>
     </row>
     <row r="60" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A60" s="13"/>
-      <c r="B60" s="14"/>
-      <c r="C60" s="14"/>
-      <c r="D60" s="14"/>
-      <c r="E60" s="14"/>
-      <c r="F60" s="14"/>
-      <c r="G60" s="14"/>
-      <c r="H60" s="14"/>
-      <c r="I60" s="15" t="str">
+      <c r="A60" s="13">
+        <v>46299</v>
+      </c>
+      <c r="B60" s="14">
+        <v>600</v>
+      </c>
+      <c r="C60" s="14">
+        <v>30</v>
+      </c>
+      <c r="D60" s="14">
+        <v>300</v>
+      </c>
+      <c r="E60" s="14">
+        <v>180</v>
+      </c>
+      <c r="F60" s="14">
+        <v>0</v>
+      </c>
+      <c r="G60" s="14">
+        <v>0</v>
+      </c>
+      <c r="H60" s="14">
+        <v>200</v>
+      </c>
+      <c r="I60" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J60" s="15" t="str">
+        <v>1310</v>
+      </c>
+      <c r="J60" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K60" s="16"/>
-      <c r="L60" s="16"/>
-      <c r="M60" s="16"/>
-      <c r="N60" s="17"/>
+        <v>130</v>
+      </c>
+      <c r="K60" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L60" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M60" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="N60" s="17" t="s">
+        <v>96</v>
+      </c>
     </row>
     <row r="61" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A61" s="13"/>

--- a/12610764.xlsx
+++ b/12610764.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{121E204C-CB79-4AA6-94AE-06DE2938597D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A4E4A3A-D869-4A33-80E8-2FF8BCEE2F5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="273" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="277" uniqueCount="97">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -3637,26 +3637,50 @@
       </c>
     </row>
     <row r="61" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A61" s="13"/>
-      <c r="B61" s="14"/>
-      <c r="C61" s="14"/>
-      <c r="D61" s="14"/>
-      <c r="E61" s="14"/>
-      <c r="F61" s="14"/>
-      <c r="G61" s="14"/>
-      <c r="H61" s="14"/>
-      <c r="I61" s="15" t="str">
+      <c r="A61" s="13">
+        <v>46300</v>
+      </c>
+      <c r="B61" s="14">
+        <v>600</v>
+      </c>
+      <c r="C61" s="14">
+        <v>30</v>
+      </c>
+      <c r="D61" s="14">
+        <v>200</v>
+      </c>
+      <c r="E61" s="14">
+        <v>60</v>
+      </c>
+      <c r="F61" s="14">
+        <v>300</v>
+      </c>
+      <c r="G61" s="14">
+        <v>6</v>
+      </c>
+      <c r="H61" s="14">
+        <v>200</v>
+      </c>
+      <c r="I61" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J61" s="15" t="str">
+        <v>1390</v>
+      </c>
+      <c r="J61" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K61" s="16"/>
-      <c r="L61" s="16"/>
-      <c r="M61" s="16"/>
-      <c r="N61" s="17"/>
+        <v>50</v>
+      </c>
+      <c r="K61" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L61" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="M61" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="N61" s="17" t="s">
+        <v>74</v>
+      </c>
     </row>
     <row r="62" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A62" s="13"/>

--- a/12610764.xlsx
+++ b/12610764.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A4E4A3A-D869-4A33-80E8-2FF8BCEE2F5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3277EB52-644A-4DAF-8269-1A8B85A5E005}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="277" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="281" uniqueCount="97">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -3683,26 +3683,50 @@
       </c>
     </row>
     <row r="62" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A62" s="13"/>
-      <c r="B62" s="14"/>
-      <c r="C62" s="14"/>
-      <c r="D62" s="14"/>
-      <c r="E62" s="14"/>
-      <c r="F62" s="14"/>
-      <c r="G62" s="14"/>
-      <c r="H62" s="14"/>
-      <c r="I62" s="15" t="str">
+      <c r="A62" s="13">
+        <v>46301</v>
+      </c>
+      <c r="B62" s="14">
+        <v>500</v>
+      </c>
+      <c r="C62" s="14">
+        <v>60</v>
+      </c>
+      <c r="D62" s="14">
+        <v>200</v>
+      </c>
+      <c r="E62" s="14">
+        <v>60</v>
+      </c>
+      <c r="F62" s="14">
+        <v>350</v>
+      </c>
+      <c r="G62" s="14">
+        <v>7</v>
+      </c>
+      <c r="H62" s="14">
+        <v>200</v>
+      </c>
+      <c r="I62" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J62" s="15" t="str">
+        <v>1370</v>
+      </c>
+      <c r="J62" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K62" s="16"/>
-      <c r="L62" s="16"/>
-      <c r="M62" s="16"/>
-      <c r="N62" s="17"/>
+        <v>70</v>
+      </c>
+      <c r="K62" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L62" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M62" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="N62" s="17" t="s">
+        <v>77</v>
+      </c>
     </row>
     <row r="63" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A63" s="13"/>

--- a/12610764.xlsx
+++ b/12610764.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3277EB52-644A-4DAF-8269-1A8B85A5E005}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2A50A2E-8838-45E0-B31F-4E049E69AB45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="281" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="97">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -3729,26 +3729,50 @@
       </c>
     </row>
     <row r="63" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A63" s="13"/>
-      <c r="B63" s="14"/>
-      <c r="C63" s="14"/>
-      <c r="D63" s="14"/>
-      <c r="E63" s="14"/>
-      <c r="F63" s="14"/>
-      <c r="G63" s="14"/>
-      <c r="H63" s="14"/>
-      <c r="I63" s="15" t="str">
+      <c r="A63" s="13">
+        <v>46302</v>
+      </c>
+      <c r="B63" s="14">
+        <v>500</v>
+      </c>
+      <c r="C63" s="14">
+        <v>30</v>
+      </c>
+      <c r="D63" s="14">
+        <v>60</v>
+      </c>
+      <c r="E63" s="14">
+        <v>120</v>
+      </c>
+      <c r="F63" s="14">
+        <v>350</v>
+      </c>
+      <c r="G63" s="14">
+        <v>7</v>
+      </c>
+      <c r="H63" s="14">
+        <v>200</v>
+      </c>
+      <c r="I63" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J63" s="15" t="str">
+        <v>1260</v>
+      </c>
+      <c r="J63" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K63" s="16"/>
-      <c r="L63" s="16"/>
-      <c r="M63" s="16"/>
-      <c r="N63" s="17"/>
+        <v>180</v>
+      </c>
+      <c r="K63" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L63" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M63" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="N63" s="17" t="s">
+        <v>74</v>
+      </c>
     </row>
     <row r="64" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A64" s="13"/>

--- a/12610764.xlsx
+++ b/12610764.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2A50A2E-8838-45E0-B31F-4E049E69AB45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9925E89B-A4BB-4C02-B5E6-F637B51E9007}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="289" uniqueCount="98">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -326,6 +326,9 @@
   </si>
   <si>
     <t>Making minor Project.</t>
+  </si>
+  <si>
+    <t>Preparation for MTT.</t>
   </si>
 </sst>
 </file>
@@ -3775,26 +3778,50 @@
       </c>
     </row>
     <row r="64" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A64" s="13"/>
-      <c r="B64" s="14"/>
-      <c r="C64" s="14"/>
-      <c r="D64" s="14"/>
-      <c r="E64" s="14"/>
-      <c r="F64" s="14"/>
-      <c r="G64" s="14"/>
-      <c r="H64" s="14"/>
-      <c r="I64" s="15" t="str">
+      <c r="A64" s="13">
+        <v>46303</v>
+      </c>
+      <c r="B64" s="14">
+        <v>400</v>
+      </c>
+      <c r="C64" s="14">
+        <v>30</v>
+      </c>
+      <c r="D64" s="14">
+        <v>120</v>
+      </c>
+      <c r="E64" s="14">
+        <v>60</v>
+      </c>
+      <c r="F64" s="14">
+        <v>150</v>
+      </c>
+      <c r="G64" s="14">
+        <v>3</v>
+      </c>
+      <c r="H64" s="14">
+        <v>200</v>
+      </c>
+      <c r="I64" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J64" s="15" t="str">
+        <v>960</v>
+      </c>
+      <c r="J64" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K64" s="16"/>
-      <c r="L64" s="16"/>
-      <c r="M64" s="16"/>
-      <c r="N64" s="17"/>
+        <v>480</v>
+      </c>
+      <c r="K64" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="L64" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="M64" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="N64" s="17" t="s">
+        <v>97</v>
+      </c>
     </row>
     <row r="65" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A65" s="13"/>

--- a/12610764.xlsx
+++ b/12610764.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9925E89B-A4BB-4C02-B5E6-F637B51E9007}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{284733D1-5335-4464-83DC-137311B0D8F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="289" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="293" uniqueCount="99">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -329,6 +329,9 @@
   </si>
   <si>
     <t>Preparation for MTT.</t>
+  </si>
+  <si>
+    <t>Today I'm very sad.</t>
   </si>
 </sst>
 </file>
@@ -3824,26 +3827,50 @@
       </c>
     </row>
     <row r="65" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A65" s="13"/>
-      <c r="B65" s="14"/>
-      <c r="C65" s="14"/>
-      <c r="D65" s="14"/>
-      <c r="E65" s="14"/>
-      <c r="F65" s="14"/>
-      <c r="G65" s="14"/>
-      <c r="H65" s="14"/>
-      <c r="I65" s="15" t="str">
+      <c r="A65" s="13">
+        <v>46304</v>
+      </c>
+      <c r="B65" s="14">
+        <v>400</v>
+      </c>
+      <c r="C65" s="14">
+        <v>30</v>
+      </c>
+      <c r="D65" s="14">
+        <v>180</v>
+      </c>
+      <c r="E65" s="14">
+        <v>60</v>
+      </c>
+      <c r="F65" s="14">
+        <v>0</v>
+      </c>
+      <c r="G65" s="14">
+        <v>0</v>
+      </c>
+      <c r="H65" s="14">
+        <v>120</v>
+      </c>
+      <c r="I65" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J65" s="15" t="str">
+        <v>790</v>
+      </c>
+      <c r="J65" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K65" s="16"/>
-      <c r="L65" s="16"/>
-      <c r="M65" s="16"/>
-      <c r="N65" s="17"/>
+        <v>650</v>
+      </c>
+      <c r="K65" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L65" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="M65" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="N65" s="17" t="s">
+        <v>98</v>
+      </c>
     </row>
     <row r="66" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A66" s="13"/>

--- a/12610764.xlsx
+++ b/12610764.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{284733D1-5335-4464-83DC-137311B0D8F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89C3D1A6-0D6D-482F-9F12-389AE83936EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="293" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="99">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -3873,26 +3873,50 @@
       </c>
     </row>
     <row r="66" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A66" s="13"/>
-      <c r="B66" s="14"/>
-      <c r="C66" s="14"/>
-      <c r="D66" s="14"/>
-      <c r="E66" s="14"/>
-      <c r="F66" s="14"/>
-      <c r="G66" s="14"/>
-      <c r="H66" s="14"/>
-      <c r="I66" s="15" t="str">
+      <c r="A66" s="13">
+        <v>46305</v>
+      </c>
+      <c r="B66" s="14">
+        <v>400</v>
+      </c>
+      <c r="C66" s="14">
+        <v>30</v>
+      </c>
+      <c r="D66" s="14">
+        <v>200</v>
+      </c>
+      <c r="E66" s="14">
+        <v>30</v>
+      </c>
+      <c r="F66" s="14">
+        <v>0</v>
+      </c>
+      <c r="G66" s="14">
+        <v>0</v>
+      </c>
+      <c r="H66" s="14">
+        <v>200</v>
+      </c>
+      <c r="I66" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J66" s="15" t="str">
+        <v>860</v>
+      </c>
+      <c r="J66" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K66" s="16"/>
-      <c r="L66" s="16"/>
-      <c r="M66" s="16"/>
-      <c r="N66" s="17"/>
+        <v>580</v>
+      </c>
+      <c r="K66" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="L66" s="16" t="s">
+        <v>73</v>
+      </c>
+      <c r="M66" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="N66" s="17" t="s">
+        <v>74</v>
+      </c>
     </row>
     <row r="67" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A67" s="13"/>

--- a/12610764.xlsx
+++ b/12610764.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89C3D1A6-0D6D-482F-9F12-389AE83936EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E7125A6-06A8-404D-90C9-B3FF07524542}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="301" uniqueCount="100">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -332,6 +332,9 @@
   </si>
   <si>
     <t>Today I'm very sad.</t>
+  </si>
+  <si>
+    <t>Cloudy day.</t>
   </si>
 </sst>
 </file>
@@ -3919,26 +3922,50 @@
       </c>
     </row>
     <row r="67" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A67" s="13"/>
-      <c r="B67" s="14"/>
-      <c r="C67" s="14"/>
-      <c r="D67" s="14"/>
-      <c r="E67" s="14"/>
-      <c r="F67" s="14"/>
-      <c r="G67" s="14"/>
-      <c r="H67" s="14"/>
-      <c r="I67" s="15" t="str">
+      <c r="A67" s="13">
+        <v>46306</v>
+      </c>
+      <c r="B67" s="14">
+        <v>400</v>
+      </c>
+      <c r="C67" s="14">
+        <v>0</v>
+      </c>
+      <c r="D67" s="14">
+        <v>300</v>
+      </c>
+      <c r="E67" s="14">
+        <v>30</v>
+      </c>
+      <c r="F67" s="14">
+        <v>0</v>
+      </c>
+      <c r="G67" s="14">
+        <v>0</v>
+      </c>
+      <c r="H67" s="14">
+        <v>30</v>
+      </c>
+      <c r="I67" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J67" s="15" t="str">
+        <v>760</v>
+      </c>
+      <c r="J67" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K67" s="16"/>
-      <c r="L67" s="16"/>
-      <c r="M67" s="16"/>
-      <c r="N67" s="17"/>
+        <v>680</v>
+      </c>
+      <c r="K67" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L67" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="M67" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="N67" s="17" t="s">
+        <v>99</v>
+      </c>
     </row>
     <row r="68" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A68" s="13"/>

--- a/12610764.xlsx
+++ b/12610764.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E7125A6-06A8-404D-90C9-B3FF07524542}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E93BCF2-1BDB-4D5B-A9FB-A9E4D7106328}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="301" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="305" uniqueCount="101">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -335,6 +335,9 @@
   </si>
   <si>
     <t>Cloudy day.</t>
+  </si>
+  <si>
+    <t>Today is 1st Mid Term.</t>
   </si>
 </sst>
 </file>
@@ -3968,26 +3971,50 @@
       </c>
     </row>
     <row r="68" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A68" s="13"/>
-      <c r="B68" s="14"/>
-      <c r="C68" s="14"/>
-      <c r="D68" s="14"/>
-      <c r="E68" s="14"/>
-      <c r="F68" s="14"/>
-      <c r="G68" s="14"/>
-      <c r="H68" s="14"/>
-      <c r="I68" s="15" t="str">
+      <c r="A68" s="13">
+        <v>46307</v>
+      </c>
+      <c r="B68" s="14">
+        <v>400</v>
+      </c>
+      <c r="C68" s="14">
+        <v>30</v>
+      </c>
+      <c r="D68" s="14">
+        <v>60</v>
+      </c>
+      <c r="E68" s="14">
+        <v>0</v>
+      </c>
+      <c r="F68" s="14">
+        <v>0</v>
+      </c>
+      <c r="G68" s="14">
+        <v>0</v>
+      </c>
+      <c r="H68" s="14">
+        <v>200</v>
+      </c>
+      <c r="I68" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J68" s="15" t="str">
+        <v>690</v>
+      </c>
+      <c r="J68" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K68" s="16"/>
-      <c r="L68" s="16"/>
-      <c r="M68" s="16"/>
-      <c r="N68" s="17"/>
+        <v>750</v>
+      </c>
+      <c r="K68" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="L68" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="M68" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="N68" s="17" t="s">
+        <v>100</v>
+      </c>
     </row>
     <row r="69" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A69" s="13"/>

--- a/12610764.xlsx
+++ b/12610764.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E93BCF2-1BDB-4D5B-A9FB-A9E4D7106328}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F913B0E9-957C-42AC-9D10-ACF4D4072742}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="305" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="309" uniqueCount="102">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -338,6 +338,9 @@
   </si>
   <si>
     <t>Today is 1st Mid Term.</t>
+  </si>
+  <si>
+    <t>Todayis 2nd Mid Term.</t>
   </si>
 </sst>
 </file>
@@ -4017,26 +4020,50 @@
       </c>
     </row>
     <row r="69" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A69" s="13"/>
-      <c r="B69" s="14"/>
-      <c r="C69" s="14"/>
-      <c r="D69" s="14"/>
-      <c r="E69" s="14"/>
-      <c r="F69" s="14"/>
-      <c r="G69" s="14"/>
-      <c r="H69" s="14"/>
-      <c r="I69" s="15" t="str">
+      <c r="A69" s="13">
+        <v>46308</v>
+      </c>
+      <c r="B69" s="14">
+        <v>400</v>
+      </c>
+      <c r="C69" s="14">
+        <v>30</v>
+      </c>
+      <c r="D69" s="14">
+        <v>60</v>
+      </c>
+      <c r="E69" s="14">
+        <v>0</v>
+      </c>
+      <c r="F69" s="14">
+        <v>0</v>
+      </c>
+      <c r="G69" s="14">
+        <v>0</v>
+      </c>
+      <c r="H69" s="14">
+        <v>200</v>
+      </c>
+      <c r="I69" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J69" s="15" t="str">
+        <v>690</v>
+      </c>
+      <c r="J69" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K69" s="16"/>
-      <c r="L69" s="16"/>
-      <c r="M69" s="16"/>
-      <c r="N69" s="17"/>
+        <v>750</v>
+      </c>
+      <c r="K69" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="L69" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="M69" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="N69" s="17" t="s">
+        <v>101</v>
+      </c>
     </row>
     <row r="70" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A70" s="13"/>

--- a/12610764.xlsx
+++ b/12610764.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F913B0E9-957C-42AC-9D10-ACF4D4072742}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3736936C-9686-412C-AD38-06FDA7AA54CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="309" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="313" uniqueCount="103">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -341,6 +341,9 @@
   </si>
   <si>
     <t>Todayis 2nd Mid Term.</t>
+  </si>
+  <si>
+    <t>Today is 3rd Mid Term.</t>
   </si>
 </sst>
 </file>
@@ -4066,26 +4069,50 @@
       </c>
     </row>
     <row r="70" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A70" s="13"/>
-      <c r="B70" s="14"/>
-      <c r="C70" s="14"/>
-      <c r="D70" s="14"/>
-      <c r="E70" s="14"/>
-      <c r="F70" s="14"/>
-      <c r="G70" s="14"/>
-      <c r="H70" s="14"/>
-      <c r="I70" s="15" t="str">
+      <c r="A70" s="13">
+        <v>46309</v>
+      </c>
+      <c r="B70" s="14">
+        <v>400</v>
+      </c>
+      <c r="C70" s="14">
+        <v>0</v>
+      </c>
+      <c r="D70" s="14">
+        <v>120</v>
+      </c>
+      <c r="E70" s="14">
+        <v>0</v>
+      </c>
+      <c r="F70" s="14">
+        <v>0</v>
+      </c>
+      <c r="G70" s="14">
+        <v>0</v>
+      </c>
+      <c r="H70" s="14">
+        <v>200</v>
+      </c>
+      <c r="I70" s="15">
         <f t="shared" ref="I70:I133" si="2">IF(SUM(B70:F70,H70)=0,"",SUM(B70:F70,H70))</f>
-        <v/>
-      </c>
-      <c r="J70" s="15" t="str">
+        <v>720</v>
+      </c>
+      <c r="J70" s="15">
         <f t="shared" ref="J70:J133" si="3">IF(I70="","",1440-I70)</f>
-        <v/>
-      </c>
-      <c r="K70" s="16"/>
-      <c r="L70" s="16"/>
-      <c r="M70" s="16"/>
-      <c r="N70" s="17"/>
+        <v>720</v>
+      </c>
+      <c r="K70" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="L70" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="M70" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="N70" s="17" t="s">
+        <v>102</v>
+      </c>
     </row>
     <row r="71" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A71" s="13"/>

--- a/12610764.xlsx
+++ b/12610764.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3736936C-9686-412C-AD38-06FDA7AA54CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08037476-B8DD-45FF-A77E-2001D444F12A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="313" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="317" uniqueCount="103">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -4115,26 +4115,50 @@
       </c>
     </row>
     <row r="71" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A71" s="13"/>
-      <c r="B71" s="14"/>
-      <c r="C71" s="14"/>
-      <c r="D71" s="14"/>
-      <c r="E71" s="14"/>
-      <c r="F71" s="14"/>
-      <c r="G71" s="14"/>
-      <c r="H71" s="14"/>
-      <c r="I71" s="15" t="str">
+      <c r="A71" s="13">
+        <v>46310</v>
+      </c>
+      <c r="B71" s="14">
+        <v>500</v>
+      </c>
+      <c r="C71" s="14">
+        <v>30</v>
+      </c>
+      <c r="D71" s="14">
+        <v>240</v>
+      </c>
+      <c r="E71" s="14">
+        <v>0</v>
+      </c>
+      <c r="F71" s="14">
+        <v>0</v>
+      </c>
+      <c r="G71" s="14">
+        <v>0</v>
+      </c>
+      <c r="H71" s="14">
+        <v>200</v>
+      </c>
+      <c r="I71" s="15">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J71" s="15" t="str">
+        <v>970</v>
+      </c>
+      <c r="J71" s="15">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K71" s="16"/>
-      <c r="L71" s="16"/>
-      <c r="M71" s="16"/>
-      <c r="N71" s="17"/>
+        <v>470</v>
+      </c>
+      <c r="K71" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="L71" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="M71" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="N71" s="17" t="s">
+        <v>74</v>
+      </c>
     </row>
     <row r="72" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A72" s="13"/>

--- a/12610764.xlsx
+++ b/12610764.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08037476-B8DD-45FF-A77E-2001D444F12A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7BE0B49F-3154-4368-986B-A8003F552E85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="317" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="321" uniqueCount="104">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -344,6 +344,9 @@
   </si>
   <si>
     <t>Today is 3rd Mid Term.</t>
+  </si>
+  <si>
+    <t>Today is 4th Mid Term.</t>
   </si>
 </sst>
 </file>
@@ -4161,26 +4164,50 @@
       </c>
     </row>
     <row r="72" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A72" s="13"/>
-      <c r="B72" s="14"/>
-      <c r="C72" s="14"/>
-      <c r="D72" s="14"/>
-      <c r="E72" s="14"/>
-      <c r="F72" s="14"/>
-      <c r="G72" s="14"/>
-      <c r="H72" s="14"/>
-      <c r="I72" s="15" t="str">
+      <c r="A72" s="13">
+        <v>46311</v>
+      </c>
+      <c r="B72" s="14">
+        <v>500</v>
+      </c>
+      <c r="C72" s="14">
+        <v>30</v>
+      </c>
+      <c r="D72" s="14">
+        <v>60</v>
+      </c>
+      <c r="E72" s="14">
+        <v>0</v>
+      </c>
+      <c r="F72" s="14">
+        <v>0</v>
+      </c>
+      <c r="G72" s="14">
+        <v>0</v>
+      </c>
+      <c r="H72" s="14">
+        <v>200</v>
+      </c>
+      <c r="I72" s="15">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J72" s="15" t="str">
+        <v>790</v>
+      </c>
+      <c r="J72" s="15">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K72" s="16"/>
-      <c r="L72" s="16"/>
-      <c r="M72" s="16"/>
-      <c r="N72" s="17"/>
+        <v>650</v>
+      </c>
+      <c r="K72" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L72" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M72" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="N72" s="17" t="s">
+        <v>103</v>
+      </c>
     </row>
     <row r="73" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A73" s="13"/>

--- a/12610764.xlsx
+++ b/12610764.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7BE0B49F-3154-4368-986B-A8003F552E85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C057B6EB-C952-431B-A7EE-9A8D54BC4FD5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="321" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="325" uniqueCount="105">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -347,6 +347,9 @@
   </si>
   <si>
     <t>Today is 4th Mid Term.</t>
+  </si>
+  <si>
+    <t>Today is last mid Term.</t>
   </si>
 </sst>
 </file>
@@ -4210,26 +4213,50 @@
       </c>
     </row>
     <row r="73" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A73" s="13"/>
-      <c r="B73" s="14"/>
-      <c r="C73" s="14"/>
-      <c r="D73" s="14"/>
-      <c r="E73" s="14"/>
-      <c r="F73" s="14"/>
-      <c r="G73" s="14"/>
-      <c r="H73" s="14"/>
-      <c r="I73" s="15" t="str">
+      <c r="A73" s="13">
+        <v>46312</v>
+      </c>
+      <c r="B73" s="14">
+        <v>500</v>
+      </c>
+      <c r="C73" s="14">
+        <v>60</v>
+      </c>
+      <c r="D73" s="14">
+        <v>120</v>
+      </c>
+      <c r="E73" s="14">
+        <v>0</v>
+      </c>
+      <c r="F73" s="14">
+        <v>0</v>
+      </c>
+      <c r="G73" s="14">
+        <v>0</v>
+      </c>
+      <c r="H73" s="14">
+        <v>200</v>
+      </c>
+      <c r="I73" s="15">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J73" s="15" t="str">
+        <v>880</v>
+      </c>
+      <c r="J73" s="15">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K73" s="16"/>
-      <c r="L73" s="16"/>
-      <c r="M73" s="16"/>
-      <c r="N73" s="17"/>
+        <v>560</v>
+      </c>
+      <c r="K73" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="L73" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="M73" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="N73" s="17" t="s">
+        <v>104</v>
+      </c>
     </row>
     <row r="74" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A74" s="13"/>

--- a/12610764.xlsx
+++ b/12610764.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C057B6EB-C952-431B-A7EE-9A8D54BC4FD5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{846A7463-2667-4C7C-9FEE-2A9130E0800B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="325" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="329" uniqueCount="105">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -4259,26 +4259,50 @@
       </c>
     </row>
     <row r="74" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A74" s="13"/>
-      <c r="B74" s="14"/>
-      <c r="C74" s="14"/>
-      <c r="D74" s="14"/>
-      <c r="E74" s="14"/>
-      <c r="F74" s="14"/>
-      <c r="G74" s="14"/>
-      <c r="H74" s="14"/>
-      <c r="I74" s="15" t="str">
+      <c r="A74" s="13">
+        <v>46313</v>
+      </c>
+      <c r="B74" s="14">
+        <v>600</v>
+      </c>
+      <c r="C74" s="14">
+        <v>30</v>
+      </c>
+      <c r="D74" s="14">
+        <v>0</v>
+      </c>
+      <c r="E74" s="14">
+        <v>0</v>
+      </c>
+      <c r="F74" s="14">
+        <v>0</v>
+      </c>
+      <c r="G74" s="14">
+        <v>0</v>
+      </c>
+      <c r="H74" s="14">
+        <v>300</v>
+      </c>
+      <c r="I74" s="15">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J74" s="15" t="str">
+        <v>930</v>
+      </c>
+      <c r="J74" s="15">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K74" s="16"/>
-      <c r="L74" s="16"/>
-      <c r="M74" s="16"/>
-      <c r="N74" s="17"/>
+        <v>510</v>
+      </c>
+      <c r="K74" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="L74" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M74" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="N74" s="17" t="s">
+        <v>74</v>
+      </c>
     </row>
     <row r="75" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A75" s="13"/>

--- a/12610764.xlsx
+++ b/12610764.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{846A7463-2667-4C7C-9FEE-2A9130E0800B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0B0671F-A3C8-49F3-B079-F88E747E9A33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="329" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="333" uniqueCount="105">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -4305,26 +4305,50 @@
       </c>
     </row>
     <row r="75" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A75" s="13"/>
-      <c r="B75" s="14"/>
-      <c r="C75" s="14"/>
-      <c r="D75" s="14"/>
-      <c r="E75" s="14"/>
-      <c r="F75" s="14"/>
-      <c r="G75" s="14"/>
-      <c r="H75" s="14"/>
-      <c r="I75" s="15" t="str">
+      <c r="A75" s="13">
+        <v>46314</v>
+      </c>
+      <c r="B75" s="14">
+        <v>600</v>
+      </c>
+      <c r="C75" s="14">
+        <v>30</v>
+      </c>
+      <c r="D75" s="14">
+        <v>0</v>
+      </c>
+      <c r="E75" s="14">
+        <v>0</v>
+      </c>
+      <c r="F75" s="14">
+        <v>0</v>
+      </c>
+      <c r="G75" s="14">
+        <v>0</v>
+      </c>
+      <c r="H75" s="14">
+        <v>300</v>
+      </c>
+      <c r="I75" s="15">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J75" s="15" t="str">
+        <v>930</v>
+      </c>
+      <c r="J75" s="15">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K75" s="16"/>
-      <c r="L75" s="16"/>
-      <c r="M75" s="16"/>
-      <c r="N75" s="17"/>
+        <v>510</v>
+      </c>
+      <c r="K75" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="L75" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="M75" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="N75" s="17" t="s">
+        <v>74</v>
+      </c>
     </row>
     <row r="76" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A76" s="13"/>

--- a/12610764.xlsx
+++ b/12610764.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0B0671F-A3C8-49F3-B079-F88E747E9A33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34141E8D-18C2-40B6-A11C-FB01D845CE51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="333" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="337" uniqueCount="105">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -4351,26 +4351,50 @@
       </c>
     </row>
     <row r="76" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A76" s="13"/>
-      <c r="B76" s="14"/>
-      <c r="C76" s="14"/>
-      <c r="D76" s="14"/>
-      <c r="E76" s="14"/>
-      <c r="F76" s="14"/>
-      <c r="G76" s="14"/>
-      <c r="H76" s="14"/>
-      <c r="I76" s="15" t="str">
+      <c r="A76" s="13">
+        <v>46315</v>
+      </c>
+      <c r="B76" s="14">
+        <v>600</v>
+      </c>
+      <c r="C76" s="14">
+        <v>60</v>
+      </c>
+      <c r="D76" s="14">
+        <v>0</v>
+      </c>
+      <c r="E76" s="14">
+        <v>0</v>
+      </c>
+      <c r="F76" s="14">
+        <v>0</v>
+      </c>
+      <c r="G76" s="14">
+        <v>0</v>
+      </c>
+      <c r="H76" s="14">
+        <v>300</v>
+      </c>
+      <c r="I76" s="15">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J76" s="15" t="str">
+        <v>960</v>
+      </c>
+      <c r="J76" s="15">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K76" s="16"/>
-      <c r="L76" s="16"/>
-      <c r="M76" s="16"/>
-      <c r="N76" s="17"/>
+        <v>480</v>
+      </c>
+      <c r="K76" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="L76" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="M76" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="N76" s="17" t="s">
+        <v>71</v>
+      </c>
     </row>
     <row r="77" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A77" s="13"/>

--- a/12610764.xlsx
+++ b/12610764.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34141E8D-18C2-40B6-A11C-FB01D845CE51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4D00F00-EEE1-403F-812D-B57AD1166E22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="337" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="341" uniqueCount="105">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -4397,26 +4397,50 @@
       </c>
     </row>
     <row r="77" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A77" s="13"/>
-      <c r="B77" s="14"/>
-      <c r="C77" s="14"/>
-      <c r="D77" s="14"/>
-      <c r="E77" s="14"/>
-      <c r="F77" s="14"/>
-      <c r="G77" s="14"/>
-      <c r="H77" s="14"/>
-      <c r="I77" s="15" t="str">
+      <c r="A77" s="13">
+        <v>46316</v>
+      </c>
+      <c r="B77" s="14">
+        <v>300</v>
+      </c>
+      <c r="C77" s="14">
+        <v>0</v>
+      </c>
+      <c r="D77" s="14">
+        <v>0</v>
+      </c>
+      <c r="E77" s="14">
+        <v>0</v>
+      </c>
+      <c r="F77" s="14">
+        <v>0</v>
+      </c>
+      <c r="G77" s="14">
+        <v>0</v>
+      </c>
+      <c r="H77" s="14">
+        <v>300</v>
+      </c>
+      <c r="I77" s="15">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J77" s="15" t="str">
+        <v>600</v>
+      </c>
+      <c r="J77" s="15">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K77" s="16"/>
-      <c r="L77" s="16"/>
-      <c r="M77" s="16"/>
-      <c r="N77" s="17"/>
+        <v>840</v>
+      </c>
+      <c r="K77" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="L77" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="M77" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="N77" s="17" t="s">
+        <v>74</v>
+      </c>
     </row>
     <row r="78" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A78" s="13"/>

--- a/12610764.xlsx
+++ b/12610764.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4D00F00-EEE1-403F-812D-B57AD1166E22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F50B1E1-C27A-48C6-8736-FC502E904E8C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="341" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="345" uniqueCount="105">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -4443,26 +4443,50 @@
       </c>
     </row>
     <row r="78" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A78" s="13"/>
-      <c r="B78" s="14"/>
-      <c r="C78" s="14"/>
-      <c r="D78" s="14"/>
-      <c r="E78" s="14"/>
-      <c r="F78" s="14"/>
-      <c r="G78" s="14"/>
-      <c r="H78" s="14"/>
-      <c r="I78" s="15" t="str">
+      <c r="A78" s="13">
+        <v>46317</v>
+      </c>
+      <c r="B78" s="14">
+        <v>300</v>
+      </c>
+      <c r="C78" s="14">
+        <v>0</v>
+      </c>
+      <c r="D78" s="14">
+        <v>0</v>
+      </c>
+      <c r="E78" s="14">
+        <v>0</v>
+      </c>
+      <c r="F78" s="14">
+        <v>0</v>
+      </c>
+      <c r="G78" s="14">
+        <v>0</v>
+      </c>
+      <c r="H78" s="14">
+        <v>600</v>
+      </c>
+      <c r="I78" s="15">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J78" s="15" t="str">
+        <v>900</v>
+      </c>
+      <c r="J78" s="15">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K78" s="16"/>
-      <c r="L78" s="16"/>
-      <c r="M78" s="16"/>
-      <c r="N78" s="17"/>
+        <v>540</v>
+      </c>
+      <c r="K78" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L78" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="M78" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="N78" s="17" t="s">
+        <v>74</v>
+      </c>
     </row>
     <row r="79" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A79" s="13"/>

--- a/12610764.xlsx
+++ b/12610764.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F50B1E1-C27A-48C6-8736-FC502E904E8C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5809501A-CE41-48D3-88DC-3CECB8EE4A4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="345" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="349" uniqueCount="105">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -4489,26 +4489,50 @@
       </c>
     </row>
     <row r="79" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A79" s="13"/>
-      <c r="B79" s="14"/>
-      <c r="C79" s="14"/>
-      <c r="D79" s="14"/>
-      <c r="E79" s="14"/>
-      <c r="F79" s="14"/>
-      <c r="G79" s="14"/>
-      <c r="H79" s="14"/>
-      <c r="I79" s="15" t="str">
+      <c r="A79" s="13">
+        <v>46318</v>
+      </c>
+      <c r="B79" s="14">
+        <v>600</v>
+      </c>
+      <c r="C79" s="14">
+        <v>0</v>
+      </c>
+      <c r="D79" s="14">
+        <v>0</v>
+      </c>
+      <c r="E79" s="14">
+        <v>0</v>
+      </c>
+      <c r="F79" s="14">
+        <v>0</v>
+      </c>
+      <c r="G79" s="14">
+        <v>0</v>
+      </c>
+      <c r="H79" s="14">
+        <v>300</v>
+      </c>
+      <c r="I79" s="15">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J79" s="15" t="str">
+        <v>900</v>
+      </c>
+      <c r="J79" s="15">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K79" s="16"/>
-      <c r="L79" s="16"/>
-      <c r="M79" s="16"/>
-      <c r="N79" s="17"/>
+        <v>540</v>
+      </c>
+      <c r="K79" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="L79" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="M79" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="N79" s="17" t="s">
+        <v>74</v>
+      </c>
     </row>
     <row r="80" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A80" s="13"/>

--- a/12610764.xlsx
+++ b/12610764.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5809501A-CE41-48D3-88DC-3CECB8EE4A4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78275601-143D-4476-AF92-9F4B6A4028D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="349" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="353" uniqueCount="106">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -350,6 +350,9 @@
   </si>
   <si>
     <t>Today is last mid Term.</t>
+  </si>
+  <si>
+    <t>At village.</t>
   </si>
 </sst>
 </file>
@@ -4535,26 +4538,50 @@
       </c>
     </row>
     <row r="80" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A80" s="13"/>
-      <c r="B80" s="14"/>
-      <c r="C80" s="14"/>
-      <c r="D80" s="14"/>
-      <c r="E80" s="14"/>
-      <c r="F80" s="14"/>
-      <c r="G80" s="14"/>
-      <c r="H80" s="14"/>
-      <c r="I80" s="15" t="str">
+      <c r="A80" s="13">
+        <v>46319</v>
+      </c>
+      <c r="B80" s="14">
+        <v>400</v>
+      </c>
+      <c r="C80" s="14">
+        <v>30</v>
+      </c>
+      <c r="D80" s="14">
+        <v>60</v>
+      </c>
+      <c r="E80" s="14">
+        <v>0</v>
+      </c>
+      <c r="F80" s="14">
+        <v>0</v>
+      </c>
+      <c r="G80" s="14">
+        <v>0</v>
+      </c>
+      <c r="H80" s="14">
+        <v>300</v>
+      </c>
+      <c r="I80" s="15">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J80" s="15" t="str">
+        <v>790</v>
+      </c>
+      <c r="J80" s="15">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K80" s="16"/>
-      <c r="L80" s="16"/>
-      <c r="M80" s="16"/>
-      <c r="N80" s="17"/>
+        <v>650</v>
+      </c>
+      <c r="K80" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="L80" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="M80" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="N80" s="17" t="s">
+        <v>105</v>
+      </c>
     </row>
     <row r="81" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A81" s="13"/>

--- a/12610764.xlsx
+++ b/12610764.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78275601-143D-4476-AF92-9F4B6A4028D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FFD69E1B-EE96-4677-ABF1-404AA4B18757}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="353" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="357" uniqueCount="107">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -353,6 +353,9 @@
   </si>
   <si>
     <t>At village.</t>
+  </si>
+  <si>
+    <t>Going to Delhi.</t>
   </si>
 </sst>
 </file>
@@ -4584,26 +4587,50 @@
       </c>
     </row>
     <row r="81" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A81" s="13"/>
-      <c r="B81" s="14"/>
-      <c r="C81" s="14"/>
-      <c r="D81" s="14"/>
-      <c r="E81" s="14"/>
-      <c r="F81" s="14"/>
-      <c r="G81" s="14"/>
-      <c r="H81" s="14"/>
-      <c r="I81" s="15" t="str">
+      <c r="A81" s="13">
+        <v>46320</v>
+      </c>
+      <c r="B81" s="14">
+        <v>400</v>
+      </c>
+      <c r="C81" s="14">
+        <v>60</v>
+      </c>
+      <c r="D81" s="14">
+        <v>120</v>
+      </c>
+      <c r="E81" s="14">
+        <v>60</v>
+      </c>
+      <c r="F81" s="14">
+        <v>0</v>
+      </c>
+      <c r="G81" s="14">
+        <v>0</v>
+      </c>
+      <c r="H81" s="14">
+        <v>300</v>
+      </c>
+      <c r="I81" s="15">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J81" s="15" t="str">
+        <v>940</v>
+      </c>
+      <c r="J81" s="15">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K81" s="16"/>
-      <c r="L81" s="16"/>
-      <c r="M81" s="16"/>
-      <c r="N81" s="17"/>
+        <v>500</v>
+      </c>
+      <c r="K81" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="L81" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M81" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="N81" s="17" t="s">
+        <v>106</v>
+      </c>
     </row>
     <row r="82" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A82" s="13"/>

--- a/12610764.xlsx
+++ b/12610764.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FFD69E1B-EE96-4677-ABF1-404AA4B18757}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4622155C-A9F0-495B-AC5E-1C7CB2FAB37C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="357" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="361" uniqueCount="107">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -4633,26 +4633,50 @@
       </c>
     </row>
     <row r="82" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A82" s="13"/>
-      <c r="B82" s="14"/>
-      <c r="C82" s="14"/>
-      <c r="D82" s="14"/>
-      <c r="E82" s="14"/>
-      <c r="F82" s="14"/>
-      <c r="G82" s="14"/>
-      <c r="H82" s="14"/>
-      <c r="I82" s="15" t="str">
+      <c r="A82" s="13">
+        <v>46321</v>
+      </c>
+      <c r="B82" s="14">
+        <v>300</v>
+      </c>
+      <c r="C82" s="14">
+        <v>0</v>
+      </c>
+      <c r="D82" s="14">
+        <v>0</v>
+      </c>
+      <c r="E82" s="14">
+        <v>0</v>
+      </c>
+      <c r="F82" s="14">
+        <v>0</v>
+      </c>
+      <c r="G82" s="14">
+        <v>0</v>
+      </c>
+      <c r="H82" s="14">
+        <v>60</v>
+      </c>
+      <c r="I82" s="15">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J82" s="15" t="str">
+        <v>360</v>
+      </c>
+      <c r="J82" s="15">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K82" s="16"/>
-      <c r="L82" s="16"/>
-      <c r="M82" s="16"/>
-      <c r="N82" s="17"/>
+        <v>1080</v>
+      </c>
+      <c r="K82" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L82" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="M82" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="N82" s="17" t="s">
+        <v>106</v>
+      </c>
     </row>
     <row r="83" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A83" s="13"/>

--- a/12610764.xlsx
+++ b/12610764.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4622155C-A9F0-495B-AC5E-1C7CB2FAB37C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9EDA3D0-B673-41A7-BA75-0BAEDB5CEB1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="361" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="365" uniqueCount="108">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -356,6 +356,9 @@
   </si>
   <si>
     <t>Going to Delhi.</t>
+  </si>
+  <si>
+    <t>Going to Phagwara.</t>
   </si>
 </sst>
 </file>
@@ -4679,26 +4682,50 @@
       </c>
     </row>
     <row r="83" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A83" s="13"/>
-      <c r="B83" s="14"/>
-      <c r="C83" s="14"/>
-      <c r="D83" s="14"/>
-      <c r="E83" s="14"/>
-      <c r="F83" s="14"/>
-      <c r="G83" s="14"/>
-      <c r="H83" s="14"/>
-      <c r="I83" s="15" t="str">
+      <c r="A83" s="13">
+        <v>46322</v>
+      </c>
+      <c r="B83" s="14">
+        <v>200</v>
+      </c>
+      <c r="C83" s="14">
+        <v>0</v>
+      </c>
+      <c r="D83" s="14">
+        <v>0</v>
+      </c>
+      <c r="E83" s="14">
+        <v>0</v>
+      </c>
+      <c r="F83" s="14">
+        <v>0</v>
+      </c>
+      <c r="G83" s="14">
+        <v>0</v>
+      </c>
+      <c r="H83" s="14">
+        <v>60</v>
+      </c>
+      <c r="I83" s="15">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J83" s="15" t="str">
+        <v>260</v>
+      </c>
+      <c r="J83" s="15">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K83" s="16"/>
-      <c r="L83" s="16"/>
-      <c r="M83" s="16"/>
-      <c r="N83" s="17"/>
+        <v>1180</v>
+      </c>
+      <c r="K83" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L83" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="M83" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="N83" s="17" t="s">
+        <v>107</v>
+      </c>
     </row>
     <row r="84" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A84" s="13"/>

--- a/12610764.xlsx
+++ b/12610764.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9EDA3D0-B673-41A7-BA75-0BAEDB5CEB1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6DB038DD-CC4F-4EA3-9C41-03EB78F7BD3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="365" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="369" uniqueCount="108">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -4728,26 +4728,50 @@
       </c>
     </row>
     <row r="84" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A84" s="13"/>
-      <c r="B84" s="14"/>
-      <c r="C84" s="14"/>
-      <c r="D84" s="14"/>
-      <c r="E84" s="14"/>
-      <c r="F84" s="14"/>
-      <c r="G84" s="14"/>
-      <c r="H84" s="14"/>
-      <c r="I84" s="15" t="str">
+      <c r="A84" s="13">
+        <v>46323</v>
+      </c>
+      <c r="B84" s="14">
+        <v>400</v>
+      </c>
+      <c r="C84" s="14">
+        <v>30</v>
+      </c>
+      <c r="D84" s="14">
+        <v>60</v>
+      </c>
+      <c r="E84" s="14">
+        <v>60</v>
+      </c>
+      <c r="F84" s="14">
+        <v>250</v>
+      </c>
+      <c r="G84" s="14">
+        <v>5</v>
+      </c>
+      <c r="H84" s="14">
+        <v>200</v>
+      </c>
+      <c r="I84" s="15">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J84" s="15" t="str">
+        <v>1000</v>
+      </c>
+      <c r="J84" s="15">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K84" s="16"/>
-      <c r="L84" s="16"/>
-      <c r="M84" s="16"/>
-      <c r="N84" s="17"/>
+        <v>440</v>
+      </c>
+      <c r="K84" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="L84" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="M84" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="N84" s="17" t="s">
+        <v>90</v>
+      </c>
     </row>
     <row r="85" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A85" s="13"/>

--- a/12610764.xlsx
+++ b/12610764.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6DB038DD-CC4F-4EA3-9C41-03EB78F7BD3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{060FB0B5-F6E6-4662-AFDB-43F80978F434}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="369" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="373" uniqueCount="108">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -4774,26 +4774,50 @@
       </c>
     </row>
     <row r="85" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A85" s="13"/>
-      <c r="B85" s="14"/>
-      <c r="C85" s="14"/>
-      <c r="D85" s="14"/>
-      <c r="E85" s="14"/>
-      <c r="F85" s="14"/>
-      <c r="G85" s="14"/>
-      <c r="H85" s="14"/>
-      <c r="I85" s="15" t="str">
+      <c r="A85" s="13">
+        <v>46324</v>
+      </c>
+      <c r="B85" s="14">
+        <v>400</v>
+      </c>
+      <c r="C85" s="14">
+        <v>30</v>
+      </c>
+      <c r="D85" s="14">
+        <v>30</v>
+      </c>
+      <c r="E85" s="14">
+        <v>30</v>
+      </c>
+      <c r="F85" s="14">
+        <v>150</v>
+      </c>
+      <c r="G85" s="14">
+        <v>3</v>
+      </c>
+      <c r="H85" s="14">
+        <v>200</v>
+      </c>
+      <c r="I85" s="15">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J85" s="15" t="str">
+        <v>840</v>
+      </c>
+      <c r="J85" s="15">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K85" s="16"/>
-      <c r="L85" s="16"/>
-      <c r="M85" s="16"/>
-      <c r="N85" s="17"/>
+        <v>600</v>
+      </c>
+      <c r="K85" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="L85" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="M85" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="N85" s="17" t="s">
+        <v>74</v>
+      </c>
     </row>
     <row r="86" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A86" s="13"/>

--- a/12610764.xlsx
+++ b/12610764.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{060FB0B5-F6E6-4662-AFDB-43F80978F434}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5837A76-9770-40BF-BD0E-46ED88B141EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="373" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="377" uniqueCount="108">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -4820,26 +4820,50 @@
       </c>
     </row>
     <row r="86" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A86" s="13"/>
-      <c r="B86" s="14"/>
-      <c r="C86" s="14"/>
-      <c r="D86" s="14"/>
-      <c r="E86" s="14"/>
-      <c r="F86" s="14"/>
-      <c r="G86" s="14"/>
-      <c r="H86" s="14"/>
-      <c r="I86" s="15" t="str">
+      <c r="A86" s="13">
+        <v>46325</v>
+      </c>
+      <c r="B86" s="14">
+        <v>400</v>
+      </c>
+      <c r="C86" s="14">
+        <v>0</v>
+      </c>
+      <c r="D86" s="14">
+        <v>60</v>
+      </c>
+      <c r="E86" s="14">
+        <v>30</v>
+      </c>
+      <c r="F86" s="14">
+        <v>250</v>
+      </c>
+      <c r="G86" s="14">
+        <v>5</v>
+      </c>
+      <c r="H86" s="14">
+        <v>200</v>
+      </c>
+      <c r="I86" s="15">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J86" s="15" t="str">
+        <v>940</v>
+      </c>
+      <c r="J86" s="15">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K86" s="16"/>
-      <c r="L86" s="16"/>
-      <c r="M86" s="16"/>
-      <c r="N86" s="17"/>
+        <v>500</v>
+      </c>
+      <c r="K86" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="L86" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M86" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="N86" s="17" t="s">
+        <v>74</v>
+      </c>
     </row>
     <row r="87" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A87" s="13"/>
